--- a/config/taa_config.xlsx
+++ b/config/taa_config.xlsx
@@ -1244,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -11170,6 +11170,73 @@
         </is>
       </c>
       <c r="M171" t="inlineStr">
+        <is>
+          <t>ewma_z</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CBOE Equity Put/Call Ratio (10d)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PCRTEQTY Index</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>EWMA z-score</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Contrarian: high PCR (&gt;1.0) = fear = buy signal for US equity; sign=+1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>PCRTEQTY Index</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t>ewma_z</t>
         </is>
@@ -12312,7 +12379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15991,6 +16058,90 @@
       <c r="F131" t="inlineStr">
         <is>
           <t>EM vs US relative PE: log(PE_US/PE_EM) — EM cheap vs US</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>us_equity</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CBOE PCR contrarian: high fear = buy signal for US equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>us_growth</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>CBOE PCR contrarian: fear drives growth premium reversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>us_value</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pcr</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CBOE PCR contrarian: fear drives value re-rating</t>
         </is>
       </c>
     </row>

--- a/config/taa_config.xlsx
+++ b/config/taa_config.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MomentumConfig" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,18 +33,21 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFC41230"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1E2E47"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -74,11 +77,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -101,11 +105,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,7 +129,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -831,6 +858,11 @@
           <t>max_tilt_pct</t>
         </is>
       </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -871,6 +903,9 @@
       <c r="H2" t="n">
         <v>2</v>
       </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -911,6 +946,9 @@
       <c r="H3" t="n">
         <v>3</v>
       </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -951,6 +989,11 @@
       <c r="H4" t="n">
         <v>4</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -991,6 +1034,11 @@
       <c r="H5" t="n">
         <v>3</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1031,6 +1079,11 @@
       <c r="H6" t="n">
         <v>3</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1071,6 +1124,11 @@
       <c r="H7" t="n">
         <v>5</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1111,6 +1169,9 @@
       <c r="H8" t="n">
         <v>3</v>
       </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1151,6 +1212,9 @@
       <c r="H9" t="n">
         <v>3</v>
       </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1191,6 +1255,11 @@
       <c r="H10" t="n">
         <v>4</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1230,6 +1299,11 @@
       </c>
       <c r="H11" t="n">
         <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7218,7 +7292,7 @@
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>inv_mom_z</t>
+          <t>diff_z</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7359,7 @@
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>inv_mom_z</t>
+          <t>diff_z</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7426,7 @@
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>inv_mom_z</t>
+          <t>diff_z</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7761,7 @@
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>inv_mom_z</t>
+          <t>diff_z</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7828,7 @@
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>inv_mom_z</t>
+          <t>diff_z</t>
         </is>
       </c>
     </row>
@@ -11268,73 +11342,73 @@
           <t>ac_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>total_check</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>money_market</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>short_term_fi</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11344,19 +11418,19 @@
           <t>lt_treasuries</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11366,19 +11440,19 @@
           <t>lt_us_corp</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11388,19 +11462,19 @@
           <t>lt_em_fi</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11410,19 +11484,19 @@
           <t>us_equity</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11432,19 +11506,19 @@
           <t>us_growth</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11454,19 +11528,19 @@
           <t>us_value</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11476,19 +11550,19 @@
           <t>dm_equity</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11498,19 +11572,19 @@
           <t>em_equity</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11529,9 +11603,9 @@
   <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20.5703125" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="127.140625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11552,136 +11626,136 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>money_market</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Macro is mostly context here - primarily used for regime detection, not direct signal.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>money_market</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>MM instruments don't have trending returns, so momentum is limited.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>money_market</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Flight to safety is the primary driver of MM demand.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>money_market</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>The dominant signal for MM is simply: is the real short-term rate positive and attractive?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>short_term_fi</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Growth/PMI signals are inverted: strong growth -&gt; rates rise -&gt; STFI price falls. Credit fundamentals remain direct (growth = tighter spreads).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>short_term_fi</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Use TR price directly. Falling prices = negative momentum. OAS tightening on short-end credits is additional carry signal.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>short_term_fi</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Flight to quality (VIX, MOVE, TED) is positive for UST/STFI. USD strength is neutral for STFI.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>short_term_fi</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Carry is the primary valuation signal. 2Y yield level and real yield determine attractiveness.</t>
         </is>
@@ -12382,7 +12456,7 @@
   <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -12522,7 +12596,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="n">
         <v>0.4</v>
@@ -12886,7 +12960,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="n">
         <v>0.2</v>
@@ -12914,7 +12988,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E19" t="n">
         <v>0.15</v>
@@ -13250,7 +13324,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E31" t="n">
         <v>0.35</v>
@@ -13278,7 +13352,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E32" t="n">
         <v>0.2</v>
@@ -13670,7 +13744,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E46" t="n">
         <v>0.4</v>
@@ -13698,7 +13772,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E47" t="n">
         <v>0.2</v>
@@ -13726,7 +13800,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E48" t="n">
         <v>0.15</v>
@@ -14062,7 +14136,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E60" t="n">
         <v>0.45</v>
@@ -14118,7 +14192,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E62" t="n">
         <v>0.2</v>
@@ -14510,7 +14584,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E76" t="n">
         <v>0.4</v>
@@ -15882,7 +15956,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E125" t="n">
         <v>0.45</v>
@@ -16157,7 +16231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16317,6 +16391,23 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>diff_z</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ewma_z(diff(window)) direction-neutral absolute change z-score</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OAS spreads Treasury yields (sign=-1 where falling=bullish)</t>
         </is>
       </c>
     </row>
